--- a/artfynd/A 68341-2021 artfynd.xlsx
+++ b/artfynd/A 68341-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 68341-2021 artfynd.xlsx
+++ b/artfynd/A 68341-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1556133</v>
+        <v>165466</v>
       </c>
       <c r="B2" t="n">
-        <v>86135</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87196</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4379</v>
+        <v>427</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Toppvaxskivling</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Cortinarius aureopulverulentus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Dalsjömotet vid väg 223, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>624428.6557564231</v>
+        <v>624429</v>
       </c>
       <c r="R2" t="n">
-        <v>6541127.473797075</v>
+        <v>6541127</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +743,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2008-10-02</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-10-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2008-10-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-10-05</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Fotbulb röd med KOH, mikroskopierad!</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,12 +762,17 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>granbevuxen källskog</t>
+          <t>granskogsravin</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,53 +790,57 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1318905</v>
+        <v>533952</v>
       </c>
       <c r="B3" t="n">
-        <v>86195</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93205</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4405</v>
+        <v>2058</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Dalsjömotet vid väg 223, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>624428.6557564231</v>
+        <v>624429</v>
       </c>
       <c r="R3" t="n">
-        <v>6541127.473797075</v>
+        <v>6541127</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,19 +867,9 @@
           <t>2008-10-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2008-10-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,62 +901,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>533952</v>
+        <v>788365</v>
       </c>
       <c r="B4" t="n">
-        <v>90660</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2058</v>
+        <v>2813</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Dalsjömotet vid väg 223, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>624428.6557564231</v>
+        <v>624429</v>
       </c>
       <c r="R4" t="n">
-        <v>6541127.473797075</v>
+        <v>6541127</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -991,19 +969,9 @@
           <t>2008-10-02</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2008-10-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,37 +1003,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1741947</v>
+        <v>1411249</v>
       </c>
       <c r="B5" t="n">
-        <v>90673</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87375</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5964</v>
+        <v>3739</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1075,13 +1038,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>624428.6557564231</v>
+        <v>624429</v>
       </c>
       <c r="R5" t="n">
-        <v>6541127.473797075</v>
+        <v>6541127</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1105,22 +1068,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2008-10-02</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-10-05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2008-10-02</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-10-05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,7 +1087,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>granbevuxen källskog</t>
+          <t>granskogsravin</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1152,15 +1105,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>788365</v>
+        <v>1556133</v>
       </c>
       <c r="B6" t="n">
-        <v>93055</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89085</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,21 +1116,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2813</v>
+        <v>4379</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1192,10 +1140,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>624428.6557564231</v>
+        <v>624429</v>
       </c>
       <c r="R6" t="n">
-        <v>6541127.473797075</v>
+        <v>6541127</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1225,19 +1173,9 @@
           <t>2008-10-02</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2008-10-02</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,37 +1207,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1411249</v>
+        <v>1318905</v>
       </c>
       <c r="B7" t="n">
-        <v>85301</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89143</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3739</v>
+        <v>4405</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1309,13 +1242,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>624428.6557564231</v>
+        <v>624429</v>
       </c>
       <c r="R7" t="n">
-        <v>6541127.473797075</v>
+        <v>6541127</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1339,22 +1272,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2012-10-05</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-10-02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2012-10-05</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-10-02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1368,7 +1291,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>granskogsravin</t>
+          <t>granbevuxen källskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1386,15 +1309,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>165466</v>
+        <v>1741947</v>
       </c>
       <c r="B8" t="n">
-        <v>85129</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1402,40 +1320,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>427</v>
+        <v>5964</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Puderspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius aureopulverulentus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Dalsjömotet vid väg 223, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>624428.6557564231</v>
+        <v>624429</v>
       </c>
       <c r="R8" t="n">
-        <v>6541127.473797075</v>
+        <v>6541127</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1459,27 +1374,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2012-10-05</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-10-02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2012-10-05</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Fotbulb röd med KOH, mikroskopierad!</t>
+          <t>2008-10-02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,17 +1388,12 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>granskogsravin</t>
+          <t>granbevuxen källskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1513,6 +1408,215 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>132283264</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57921</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100067</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Havsörn</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Haliaeetus albicilla</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Stene, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>624327</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6541161</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Björnlunda</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>flög upp framför bilen efter att ha vilat på landsvägen</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>landsväg</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126635192</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Stene nära väg 223, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>624342</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6541167</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Björnlunda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>vägkant</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 68341-2021 artfynd.xlsx
+++ b/artfynd/A 68341-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/165466</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/533952</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1000,6 +1015,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/788365</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1102,6 +1122,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1411249</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1204,6 +1229,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1556133</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1306,6 +1336,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1318905</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1408,6 +1443,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1741947</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1515,6 +1555,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132283264</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1617,8 +1662,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126635192</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>